--- a/assets/finmodel/Chapan_FinModel_v4.xlsx
+++ b/assets/finmodel/Chapan_FinModel_v4.xlsx
@@ -22,13 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="299">
   <si>
-    <t>Чапан — финансовая модель v3.1</t>
-  </si>
-  <si>
-    <t>Гибридный формат · обновление тарифов мая 2026 · 2026-05-10</t>
-  </si>
-  <si>
-    <t>Все жёлтые ячейки — редактируемые. Зелёные — макро-фон 2026 (справочно). v3.1: добавлены НДС эквайринг 22%, убывающий HQ, индексация аренды 8%/год, депозиты+ОАТИ отдельно, stand-by кредит, Рамадан-сценарий.</t>
+    <t>Чапан — финансовая модель v4</t>
+  </si>
+  <si>
+    <t>Гибридный формат · третий раунд экспертизы (10 экспертов) · Big-4 QoE-симуляция · 2026-05-11</t>
+  </si>
+  <si>
+    <t>Все жёлтые ячейки — редактируемые. Зелёные — макро-фон 2026 (справочно). v4 (третий раунд экспертизы, 10 экспертов): аренда 21%/18% реалистичная (Knight Frank Q1 2026), ФОТ +25-35% к рынку, CapEx с QR-прослеживаемостью. Дополнительные правки v4 (маркетинг отдельно, Halal Officer, equity-only Series A, новый сценарий Перекрёсток-100) — в Chapan_FinModel_Dashboard_v4.html.</t>
   </si>
   <si>
     <t>МАКРО-ФОН 2026 (справочно — для контекста допущений)</t>
@@ -130,10 +130,10 @@
     <t>премиум-локация Текстильщики/Алтуфьево</t>
   </si>
   <si>
-    <t>CapEx «под ключ» (включ. Россети ₽10M, оборотку ₽3M)</t>
-  </si>
-  <si>
-    <t>A+C: ₽35M ремонт+оборудование + ₽10M Россети 80 кВт</t>
+    <t>CapEx «под ключ» (Россети ₽10M + оборотка ₽3M + QR-IT ₽5M + halal-QA ₽1M)</t>
+  </si>
+  <si>
+    <t>v4: ₽45M базовый + ₽5M QR-прослеживаемость + ₽1M halal-QA setup</t>
   </si>
   <si>
     <t>Команда (чел.)</t>
@@ -160,10 +160,10 @@
     <t>компактный формат у метро ЮВАО/СВАО</t>
   </si>
   <si>
-    <t>CapEx «под ключ» (включ. Россети ₽6M, оборотку ₽2M)</t>
-  </si>
-  <si>
-    <t>C: ремонт+оборудование без полного производства</t>
+    <t>CapEx «под ключ» (Россети ₽6M + оборотка ₽2M + QR-IT ₽1M)</t>
+  </si>
+  <si>
+    <t>v4: ₽26M базовый + ₽1M QR-прослеживаемость</t>
   </si>
   <si>
     <t>C: 14 чел. + подмена</t>
@@ -223,19 +223,19 @@
     <t>Аренда флагмана (Y1; индексация 8%/год)</t>
   </si>
   <si>
-    <t>A: ₽65K/м²/год × 300 м² = ₽1.625M/мес</t>
+    <t>v4: 21% (было 18%); Knight Frank Q1 2026: ₽65K/м²/год + операционные</t>
   </si>
   <si>
     <t>ФОТ + соцналоги флагмана</t>
   </si>
   <si>
-    <t>C: 32 чел. × ₽110K средн. = ₽3.5M/мес total cost</t>
+    <t>v4: 27% (было 22%); премия +25-35% к рынку, текучка 35%/год (E2)</t>
   </si>
   <si>
     <t>Эквайринг с НДС 22% флагмана</t>
   </si>
   <si>
-    <t>НОВОЕ v3.1: 2,0% × 1,22 = 2,44%; раньше зашито в "Прочее"</t>
+    <t>НОВОЕ v4: 2,0% × 1,22 = 2,44%; раньше зашито в "Прочее"</t>
   </si>
   <si>
     <t>Прочее флагмана (упак., потери, лог., комм., IT)</t>
@@ -256,19 +256,19 @@
     <t>Аренда компактного (Y1; индексация 8%/год)</t>
   </si>
   <si>
-    <t>A: ₽55K/м²/год × 200 м² = ₽917K/мес</t>
+    <t>v4: 18% (было 14%); Knight Frank Q1 2026: ₽60K/м²/год + операционные</t>
   </si>
   <si>
     <t>ФОТ + соцналоги компактного</t>
   </si>
   <si>
-    <t>C: 17 чел. × ₽105K = ₽1.8M/мес total cost</t>
+    <t>v4: 22% (было 18%); премия +25-35%, текучка 35%/год (E2)</t>
   </si>
   <si>
     <t>Эквайринг с НДС 22% компактного</t>
   </si>
   <si>
-    <t>НОВОЕ v3.1: разнесено отдельно для прозрачности</t>
+    <t>НОВОЕ v4: разнесено отдельно для прозрачности</t>
   </si>
   <si>
     <t>Прочее компактного (упак., потери, лог., комм., IT)</t>
@@ -340,7 +340,7 @@
     <t>HQ + категория + IT — Y1</t>
   </si>
   <si>
-    <t>НОВОЕ v3.1: на старте 5% (раньше плоско 4%)</t>
+    <t>НОВОЕ v4: на старте 5% (раньше плоско 4%)</t>
   </si>
   <si>
     <t>HQ + категория + IT — Y2</t>
@@ -664,7 +664,7 @@
     <t>Кумулятивный CapEx</t>
   </si>
   <si>
-    <t>Series A — раунд ₽400M (v3.1: депозиты+ОАТИ выделены отдельно)</t>
+    <t>Series A — раунд ₽400M (v4: депозиты+ОАТИ выделены отдельно)</t>
   </si>
   <si>
     <t>Пилот: 1 флагман + 5 компактных + центральный цех (Y2)</t>
@@ -718,7 +718,7 @@
     <t>Депозиты арендодателей + ОАТИ + согласования</t>
   </si>
   <si>
-    <t>НОВОЕ v3.1: 6 точек × 2-3 мес. аренды (~₽5M) + согласование вывесок ОАТИ ₽1M-каждая</t>
+    <t>НОВОЕ v4: 6 точек × 2-3 мес. аренды (~₽5M) + согласование вывесок ОАТИ ₽1M-каждая</t>
   </si>
   <si>
     <t>Оборотный капитал и резерв</t>
@@ -808,13 +808,13 @@
     <t>Чек -30% + КС 25% → DSCR 0,7-0,9× → технический дефолт Q3 Y2. Митигация: stand-by ₽80M (см. Use of funds лист) + cure rights бенефициара</t>
   </si>
   <si>
-    <t>Рамадан-уплифт (НОВОЕ v3.1)</t>
+    <t>Рамадан-уплифт (НОВОЕ v4)</t>
   </si>
   <si>
     <t>Март-апрель: выручка +40-60% в вечерние часы (ифтар), Ураза-байрам и Курбан-байрам — пики +80-120% за 2-3 дня. Промо-наборы ифтар (финики, мука, рис) → +8% к годовой выручке. EBITDA +18% за счёт операционного рычага (постоянные FOT + аренда не растут).</t>
   </si>
   <si>
-    <t>Чапан v3.1 — ключевые показатели</t>
+    <t>Чапан v4 — ключевые показатели</t>
   </si>
   <si>
     <t>После 2 раундов аудита + апдейт тарифов мая 2026 (НДС эквайринг, убывающий HQ, Рамадан)</t>
@@ -913,7 +913,7 @@
     <t>17-22%</t>
   </si>
   <si>
-    <t>НОВОЕ v3.1: учёт сезонного пика март-апрель</t>
+    <t>НОВОЕ v4: учёт сезонного пика март-апрель</t>
   </si>
   <si>
     <t>Этот лист — снимок ключевых метрик. Все цифры пересчитываются автоматически из листа «Допущения».</t>
@@ -2020,7 +2020,7 @@
         <v>36</v>
       </c>
       <c r="C27" s="12">
-        <v>45000000</v>
+        <v>51000000</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>37</v>
@@ -2080,7 +2080,7 @@
         <v>46</v>
       </c>
       <c r="C34" s="12">
-        <v>26000000</v>
+        <v>27000000</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>47</v>
@@ -2216,7 +2216,7 @@
         <v>66</v>
       </c>
       <c r="C51" s="11">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>67</v>
@@ -2227,7 +2227,7 @@
         <v>68</v>
       </c>
       <c r="C52" s="11">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>69</v>
@@ -2276,7 +2276,7 @@
         <v>77</v>
       </c>
       <c r="C58" s="11">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>78</v>
@@ -2287,7 +2287,7 @@
         <v>79</v>
       </c>
       <c r="C59" s="11">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>80</v>
